--- a/新建 XLSX 工作表.xlsx
+++ b/新建 XLSX 工作表.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="246">
   <si>
     <t>标签</t>
   </si>
@@ -479,7 +479,7 @@
     <t>决定了按钮被点击时执行的函数</t>
   </si>
   <si>
-    <t>目前只支持内置函数,详见A81</t>
+    <t>目前只支持内置函数,详见A120</t>
   </si>
   <si>
     <t>&lt;button onclick="openUIByFilePath(kubejs/mcml/aabb.mcml)" /&gt;</t>
@@ -861,6 +861,18 @@
   </si>
   <si>
     <t>默认值为#BE961C</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>样式表标签</t>
+  </si>
+  <si>
+    <t>recipe</t>
+  </si>
+  <si>
+    <t>配方标签</t>
   </si>
   <si>
     <t>通用标签属性</t>
@@ -1110,12 +1122,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1667,7 +1679,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1812,27 +1824,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1846,9 +1837,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -2216,7 +2204,7 @@
       <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -2235,7 +2223,7 @@
       <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="6"/>
@@ -2383,7 +2371,7 @@
       <c r="E11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="F11" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="12" t="s">
@@ -2417,7 +2405,7 @@
       <c r="E13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="12" t="s">
@@ -2527,7 +2515,7 @@
       <c r="E19" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="51" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -2559,7 +2547,7 @@
       <c r="E21" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -2578,7 +2566,7 @@
       <c r="E22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -2597,7 +2585,7 @@
       <c r="E23" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="56" t="s">
+      <c r="F23" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -2635,7 +2623,7 @@
       <c r="E25" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="5" t="s">
@@ -2654,7 +2642,7 @@
       <c r="E26" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="56" t="s">
+      <c r="F26" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -2764,7 +2752,7 @@
       <c r="E32" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="12" t="s">
@@ -2783,7 +2771,7 @@
       <c r="E33" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="12" t="s">
@@ -2802,7 +2790,7 @@
       <c r="E34" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="12" t="s">
@@ -2840,7 +2828,7 @@
       <c r="E36" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="F36" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="11" t="s">
@@ -2859,7 +2847,7 @@
       <c r="E37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="12" t="s">
@@ -3005,7 +2993,7 @@
       <c r="E45" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F45" s="56" t="s">
+      <c r="F45" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="6" t="s">
@@ -3024,7 +3012,7 @@
       <c r="E46" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="56" t="s">
+      <c r="F46" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="6" t="s">
@@ -3043,7 +3031,7 @@
       <c r="E47" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F47" s="56" t="s">
+      <c r="F47" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="6" t="s">
@@ -3153,7 +3141,7 @@
       <c r="E53" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="12" t="s">
@@ -3191,7 +3179,7 @@
       <c r="E55" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="57" t="s">
+      <c r="F55" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="12" t="s">
@@ -3210,7 +3198,7 @@
       <c r="E56" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F56" s="57" t="s">
+      <c r="F56" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="12" t="s">
@@ -3229,7 +3217,7 @@
       <c r="E57" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="F57" s="57" t="s">
+      <c r="F57" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="12" t="s">
@@ -3339,7 +3327,7 @@
       <c r="E63" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="56" t="s">
+      <c r="F63" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="6" t="s">
@@ -3358,7 +3346,7 @@
       <c r="E64" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F64" s="56" t="s">
+      <c r="F64" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="6" t="s">
@@ -3377,7 +3365,7 @@
       <c r="E65" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="F65" s="56" t="s">
+      <c r="F65" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G65" s="6" t="s">
@@ -3415,7 +3403,7 @@
       <c r="E67" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="F67" s="59" t="s">
+      <c r="F67" s="52" t="s">
         <v>12</v>
       </c>
       <c r="G67" s="32" t="s">
@@ -3434,7 +3422,7 @@
       <c r="E68" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="F68" s="59" t="s">
+      <c r="F68" s="52" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="32" t="s">
@@ -3453,7 +3441,7 @@
       <c r="E69" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F69" s="56" t="s">
+      <c r="F69" s="49" t="s">
         <v>12</v>
       </c>
       <c r="G69" s="6" t="s">
@@ -3606,7 +3594,7 @@
       <c r="E78" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="F78" s="57" t="s">
+      <c r="F78" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="12" t="s">
@@ -3625,7 +3613,7 @@
       <c r="E79" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="F79" s="57" t="s">
+      <c r="F79" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="12" t="s">
@@ -3774,7 +3762,7 @@
       <c r="E88" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="F88" s="57" t="s">
+      <c r="F88" s="50" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="12" t="s">
@@ -3869,285 +3857,301 @@
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="48" t="s">
+      <c r="A94" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B94" s="49" t="s">
+      <c r="B94" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C94" s="48" t="s">
+      <c r="C94" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D94" s="50" t="s">
+      <c r="D94" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E94" s="51" t="s">
+      <c r="E94" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="F94" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G94" s="48" t="s">
+      <c r="F94" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="48"/>
-      <c r="B95" s="49"/>
-      <c r="C95" s="48"/>
-      <c r="D95" s="50" t="s">
+      <c r="A95" s="6"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E95" s="51"/>
-      <c r="F95" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="48" t="s">
+      <c r="E95" s="8"/>
+      <c r="F95" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="48"/>
-      <c r="B96" s="49"/>
-      <c r="C96" s="48"/>
-      <c r="D96" s="50" t="s">
+      <c r="A96" s="6"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="E96" s="51"/>
-      <c r="F96" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" s="48" t="s">
+      <c r="E96" s="8"/>
+      <c r="F96" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="97" ht="40.5" spans="1:7">
-      <c r="A97" s="48"/>
-      <c r="B97" s="49"/>
-      <c r="C97" s="48" t="s">
+      <c r="A97" s="6"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D97" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="51" t="s">
+      <c r="D97" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="F97" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" s="48" t="s">
+      <c r="F97" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:7">
-      <c r="A98" s="48"/>
-      <c r="B98" s="49"/>
-      <c r="C98" s="48" t="s">
+      <c r="A98" s="6"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="6" t="s">
         <v>194</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E98" s="51" t="s">
+      <c r="E98" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F98" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" s="52" t="s">
+      <c r="F98" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="17" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="99" ht="27" spans="1:7">
-      <c r="A99" s="48"/>
-      <c r="B99" s="49"/>
-      <c r="C99" s="48" t="s">
+      <c r="A99" s="6"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="6" t="s">
         <v>197</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E99" s="51" t="s">
+      <c r="E99" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F99" s="49" t="s">
+      <c r="F99" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G99" s="53"/>
+      <c r="G99" s="26"/>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="48"/>
-      <c r="B100" s="49"/>
-      <c r="C100" s="48" t="s">
+      <c r="A100" s="6"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="6" t="s">
         <v>201</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E100" s="51" t="s">
+      <c r="E100" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F100" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="53"/>
+      <c r="F100" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="26"/>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="48"/>
-      <c r="B101" s="49"/>
-      <c r="C101" s="48" t="s">
+      <c r="A101" s="6"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="6" t="s">
         <v>203</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E101" s="51" t="s">
+      <c r="E101" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="F101" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G101" s="53"/>
+      <c r="F101" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="26"/>
     </row>
     <row r="102" spans="1:7">
-      <c r="A102" s="48"/>
-      <c r="B102" s="49"/>
-      <c r="C102" s="48" t="s">
+      <c r="A102" s="6"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="6" t="s">
         <v>206</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E102" s="51" t="s">
+      <c r="E102" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="F102" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G102" s="53"/>
+      <c r="F102" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="26"/>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="48"/>
-      <c r="B103" s="49"/>
-      <c r="C103" s="48" t="s">
+      <c r="A103" s="6"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="6" t="s">
         <v>209</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="E103" s="51" t="s">
+      <c r="E103" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F103" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G103" s="53"/>
+      <c r="F103" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" s="26"/>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="48"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="48" t="s">
+      <c r="A104" s="6"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="6" t="s">
         <v>212</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E104" s="51" t="s">
+      <c r="E104" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F104" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G104" s="53"/>
+      <c r="F104" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="26"/>
     </row>
     <row r="105" spans="1:7">
-      <c r="A105" s="48"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="48" t="s">
+      <c r="A105" s="6"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="6" t="s">
         <v>214</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E105" s="51" t="s">
+      <c r="E105" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F105" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="54"/>
+      <c r="F105" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="20"/>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D112" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D113" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" ht="27" spans="1:7">
       <c r="A116" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D116" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" ht="40.5" spans="1:7">
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D117" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4155,39 +4159,39 @@
         <v>106</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D120" s="55" t="s">
-        <v>236</v>
+        <v>239</v>
+      </c>
+      <c r="D120" s="48" t="s">
+        <v>240</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F120" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="F120" s="53" t="s">
         <v>12</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="C121" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D121" s="55" t="s">
-        <v>240</v>
+        <v>243</v>
+      </c>
+      <c r="D121" s="48" t="s">
+        <v>244</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F121" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="F121" s="53" t="s">
         <v>12</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4244,7 +4248,7 @@
     <mergeCell ref="A116:B117"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F44" location="Sheet1!A81" display="目前只支持内置函数,详见A81"/>
+    <hyperlink ref="F44" location="Sheet1!A120" display="目前只支持内置函数,详见A120"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
